--- a/data/config/luban/config/general/frame.xlsx
+++ b/data/config/luban/config/general/frame.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Item" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Item!$A$3:$C$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Item!$A$3:$C$11</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="36">
   <si>
     <t>##var</t>
   </si>
@@ -119,7 +119,25 @@
     <t>属性加成</t>
   </si>
   <si>
-    <t>默认头像</t>
+    <t>默认头像框</t>
+  </si>
+  <si>
+    <t>白</t>
+  </si>
+  <si>
+    <t>绿</t>
+  </si>
+  <si>
+    <t>蓝</t>
+  </si>
+  <si>
+    <t>紫</t>
+  </si>
+  <si>
+    <t>橙</t>
+  </si>
+  <si>
+    <t>红</t>
   </si>
 </sst>
 </file>
@@ -1307,8 +1325,8 @@
   <sheetPr codeName="Sheet1">
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:K5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelRow="4"/>
+  <dimension ref="A1:K10"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="32.8833333333333" style="2" customWidth="1"/>
     <col min="2" max="2" width="18.125" style="2" customWidth="1"/>
@@ -1452,17 +1470,163 @@
       </c>
     </row>
     <row r="5" spans="1:11">
-      <c r="D5" s="2" t="str">
+      <c r="B5" s="2">
+        <v>5011002</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5" s="2">
         <f>IF(B5="","",MOD(INT(B5/1000),10))</f>
-        <v/>
-      </c>
-      <c r="E5" s="2" t="str">
+        <v>1</v>
+      </c>
+      <c r="E5" s="2">
         <f>IF(B5="","",MOD(INT(B5/10000),10))</f>
-        <v/>
+        <v>1</v>
+      </c>
+      <c r="F5" s="2" t="str">
+        <f t="shared" ref="F5:F10" si="0">"Assets/Game/Textures/Frame/"&amp;B5&amp;".png"</f>
+        <v>Assets/Game/Textures/Frame/5011002.png</v>
+      </c>
+      <c r="H5" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I5" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="B6" s="2">
+        <v>5011003</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6" s="2">
+        <f>IF(B6="","",MOD(INT(B6/1000),10))</f>
+        <v>1</v>
+      </c>
+      <c r="E6" s="2">
+        <f>IF(B6="","",MOD(INT(B6/10000),10))</f>
+        <v>1</v>
+      </c>
+      <c r="F6" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>Assets/Game/Textures/Frame/5011003.png</v>
+      </c>
+      <c r="H6" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I6" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="B7" s="2">
+        <v>5011004</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7" s="2">
+        <f>IF(B7="","",MOD(INT(B7/1000),10))</f>
+        <v>1</v>
+      </c>
+      <c r="E7" s="2">
+        <f>IF(B7="","",MOD(INT(B7/10000),10))</f>
+        <v>1</v>
+      </c>
+      <c r="F7" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>Assets/Game/Textures/Frame/5011004.png</v>
+      </c>
+      <c r="H7" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I7" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="B8" s="2">
+        <v>5011005</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D8" s="2">
+        <f>IF(B8="","",MOD(INT(B8/1000),10))</f>
+        <v>1</v>
+      </c>
+      <c r="E8" s="2">
+        <f>IF(B8="","",MOD(INT(B8/10000),10))</f>
+        <v>1</v>
+      </c>
+      <c r="F8" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>Assets/Game/Textures/Frame/5011005.png</v>
+      </c>
+      <c r="H8" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I8" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="B9" s="2">
+        <v>5011006</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" s="2">
+        <f>IF(B9="","",MOD(INT(B9/1000),10))</f>
+        <v>1</v>
+      </c>
+      <c r="E9" s="2">
+        <f>IF(B9="","",MOD(INT(B9/10000),10))</f>
+        <v>1</v>
+      </c>
+      <c r="F9" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>Assets/Game/Textures/Frame/5011006.png</v>
+      </c>
+      <c r="H9" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I9" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="B10" s="2">
+        <v>5011007</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D10" s="2">
+        <f>IF(B10="","",MOD(INT(B10/1000),10))</f>
+        <v>1</v>
+      </c>
+      <c r="E10" s="2">
+        <f>IF(B10="","",MOD(INT(B10/10000),10))</f>
+        <v>1</v>
+      </c>
+      <c r="F10" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>Assets/Game/Textures/Frame/5011007.png</v>
+      </c>
+      <c r="H10" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I10" s="2" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A3:C5" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A3:C11" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <conditionalFormatting sqref="D3">

--- a/data/config/luban/config/general/frame.xlsx
+++ b/data/config/luban/config/general/frame.xlsx
@@ -122,22 +122,22 @@
     <t>默认头像框</t>
   </si>
   <si>
-    <t>白</t>
-  </si>
-  <si>
-    <t>绿</t>
-  </si>
-  <si>
-    <t>蓝</t>
-  </si>
-  <si>
-    <t>紫</t>
-  </si>
-  <si>
-    <t>橙</t>
-  </si>
-  <si>
-    <t>红</t>
+    <t>头像框-白</t>
+  </si>
+  <si>
+    <t>头像框-绿</t>
+  </si>
+  <si>
+    <t>头像框-蓝</t>
+  </si>
+  <si>
+    <t>头像框-紫</t>
+  </si>
+  <si>
+    <t>头像框-橙</t>
+  </si>
+  <si>
+    <t>头像框-红</t>
   </si>
 </sst>
 </file>
@@ -1451,11 +1451,11 @@
         <v>29</v>
       </c>
       <c r="D4" s="2">
-        <f>IF(B4="","",MOD(INT(B4/1000),10))</f>
+        <f t="shared" ref="D4:D10" si="0">IF(B4="","",MOD(INT(B4/1000),10))</f>
         <v>1</v>
       </c>
       <c r="E4" s="2">
-        <f>IF(B4="","",MOD(INT(B4/10000),10))</f>
+        <f t="shared" ref="E4:E10" si="1">IF(B4="","",MOD(INT(B4/10000),10))</f>
         <v>1</v>
       </c>
       <c r="F4" s="2" t="str">
@@ -1477,15 +1477,15 @@
         <v>30</v>
       </c>
       <c r="D5" s="2">
-        <f>IF(B5="","",MOD(INT(B5/1000),10))</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="E5" s="2">
-        <f>IF(B5="","",MOD(INT(B5/10000),10))</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="F5" s="2" t="str">
-        <f t="shared" ref="F5:F10" si="0">"Assets/Game/Textures/Frame/"&amp;B5&amp;".png"</f>
+        <f t="shared" ref="F5:F10" si="2">"Assets/Game/Textures/Frame/"&amp;B5&amp;".png"</f>
         <v>Assets/Game/Textures/Frame/5011002.png</v>
       </c>
       <c r="H5" s="2" t="b">
@@ -1503,15 +1503,15 @@
         <v>31</v>
       </c>
       <c r="D6" s="2">
-        <f>IF(B6="","",MOD(INT(B6/1000),10))</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="E6" s="2">
-        <f>IF(B6="","",MOD(INT(B6/10000),10))</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="F6" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>Assets/Game/Textures/Frame/5011003.png</v>
       </c>
       <c r="H6" s="2" t="b">
@@ -1529,15 +1529,15 @@
         <v>32</v>
       </c>
       <c r="D7" s="2">
-        <f>IF(B7="","",MOD(INT(B7/1000),10))</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="E7" s="2">
-        <f>IF(B7="","",MOD(INT(B7/10000),10))</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="F7" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>Assets/Game/Textures/Frame/5011004.png</v>
       </c>
       <c r="H7" s="2" t="b">
@@ -1555,15 +1555,15 @@
         <v>33</v>
       </c>
       <c r="D8" s="2">
-        <f>IF(B8="","",MOD(INT(B8/1000),10))</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="E8" s="2">
-        <f>IF(B8="","",MOD(INT(B8/10000),10))</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="F8" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>Assets/Game/Textures/Frame/5011005.png</v>
       </c>
       <c r="H8" s="2" t="b">
@@ -1581,15 +1581,15 @@
         <v>34</v>
       </c>
       <c r="D9" s="2">
-        <f>IF(B9="","",MOD(INT(B9/1000),10))</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="E9" s="2">
-        <f>IF(B9="","",MOD(INT(B9/10000),10))</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="F9" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>Assets/Game/Textures/Frame/5011006.png</v>
       </c>
       <c r="H9" s="2" t="b">
@@ -1607,15 +1607,15 @@
         <v>35</v>
       </c>
       <c r="D10" s="2">
-        <f>IF(B10="","",MOD(INT(B10/1000),10))</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="E10" s="2">
-        <f>IF(B10="","",MOD(INT(B10/10000),10))</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="F10" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>Assets/Game/Textures/Frame/5011007.png</v>
       </c>
       <c r="H10" s="2" t="b">
